--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45614</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45428</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45629</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>45119</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>45356</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>44526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>45119</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         <v>45202</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>46198</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>45756</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44957</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45820</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>45834</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44902</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         <v>45471</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>45553</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45429</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>45937</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>46047</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>45418</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>44878</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>44855</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45534</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4971,7 +4971,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>45302</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
         <v>45945</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>46150</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5616,7 +5616,7 @@
         <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         <v>45057</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6051,7 +6051,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
         <v>46209</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6271,7 +6271,7 @@
         <v>46261</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>45198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>45807</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
         <v>46240</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
         <v>46258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7151,7 +7151,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7224,7 +7224,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>44629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7380,7 +7380,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7453,7 +7453,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         <v>44851</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7755,7 +7755,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
         <v>44465</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7906,7 +7906,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>45170</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45622</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45556</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45330</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45721</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45257</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44876</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45036</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>45446</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45491</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8807,7 +8807,7 @@
         <v>45125</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8880,7 +8880,7 @@
         <v>45125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         <v>45714</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9182,7 +9182,7 @@
         <v>44860</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>45461</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         <v>45547</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9411,7 +9411,7 @@
         <v>45735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9489,7 +9489,7 @@
         <v>45036</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45742</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>45351</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>45198</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>45228</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>45228</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44582</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>45013</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10093,7 +10093,7 @@
         <v>45586</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45720</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10249,7 +10249,7 @@
         <v>45356</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10322,7 +10322,7 @@
         <v>45471</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44742</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10473,7 +10473,7 @@
         <v>45331</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>45705</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>46139</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10770,7 +10770,7 @@
         <v>45351</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10848,7 +10848,7 @@
         <v>46136</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>45140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45891</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>46010</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11223,7 +11223,7 @@
         <v>45893</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11301,7 +11301,7 @@
         <v>45142</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>45978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11447,7 +11447,7 @@
         <v>45988</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>45855</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>45898</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>45483</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>45757</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>45098</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>45903</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11978,7 +11978,7 @@
         <v>46136</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>45611</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>45905</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>45904</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>46136</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45295</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46141</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12504,7 +12504,7 @@
         <v>45876</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44974</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12655,7 +12655,7 @@
         <v>45912</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12733,7 +12733,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12811,7 +12811,7 @@
         <v>46136</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>46141</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12957,7 +12957,7 @@
         <v>45915</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>45912</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13191,7 +13191,7 @@
         <v>46140</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13269,7 +13269,7 @@
         <v>45770</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45917</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45916</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45916</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45917</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>46141</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13732,7 +13732,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>45614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>46013</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13956,7 +13956,7 @@
         <v>45845</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>45639</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14107,7 +14107,7 @@
         <v>45845</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14180,7 +14180,7 @@
         <v>45672</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45253</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14331,7 +14331,7 @@
         <v>46136</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>45642</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>45678</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14550,7 +14550,7 @@
         <v>45866</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14628,7 +14628,7 @@
         <v>44971</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14701,7 +14701,7 @@
         <v>45720</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14779,7 +14779,7 @@
         <v>45936</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>45936</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14925,7 +14925,7 @@
         <v>45936</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15003,7 +15003,7 @@
         <v>46146</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>44925</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15154,7 +15154,7 @@
         <v>46147</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>45938</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45937</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46146</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15466,7 +15466,7 @@
         <v>46147</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45069</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45614</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>46189</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>46189</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45642</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>46189</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>45539</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16060,7 +16060,7 @@
         <v>45224</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45574</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45463</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>46149</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45747</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16523,7 +16523,7 @@
         <v>45217</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16596,7 +16596,7 @@
         <v>44974</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16669,7 +16669,7 @@
         <v>44956</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>46150</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>46153</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45959</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46150</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>46153</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45965</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17293,7 +17293,7 @@
         <v>46155</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45561</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45642</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17522,7 +17522,7 @@
         <v>45642</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17678,7 +17678,7 @@
         <v>45966</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45975</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45975</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45977</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17990,7 +17990,7 @@
         <v>44568</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18063,7 +18063,7 @@
         <v>45978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18136,7 +18136,7 @@
         <v>45729</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18214,7 +18214,7 @@
         <v>45978</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44888</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18438,7 +18438,7 @@
         <v>45980</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
         <v>45980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18594,7 +18594,7 @@
         <v>45981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18667,7 +18667,7 @@
         <v>45981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45982</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44960</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>45982</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>45986</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>45882</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>46107</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19198,7 +19198,7 @@
         <v>45161</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19276,7 +19276,7 @@
         <v>45988</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>45505</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19500,7 +19500,7 @@
         <v>45988</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>45516</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>44980</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45475</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>46160</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19875,7 +19875,7 @@
         <v>45448</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45491</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45071</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45962</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>46162</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>46162</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45399</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>44889</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45862</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44524</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45996</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20698,7 +20698,7 @@
         <v>46162</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20776,7 +20776,7 @@
         <v>46162</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>45600</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>46003</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>46003</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21078,7 +21078,7 @@
         <v>46007</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21151,7 +21151,7 @@
         <v>46007</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>46007</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45755</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>46007</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45552</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46009</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21599,7 +21599,7 @@
         <v>45539</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45149</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21750,7 +21750,7 @@
         <v>44979</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>46010</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21901,7 +21901,7 @@
         <v>44761</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>46017</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22052,7 +22052,7 @@
         <v>45036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22125,7 +22125,7 @@
         <v>45520</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22198,7 +22198,7 @@
         <v>45392</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22276,7 +22276,7 @@
         <v>44719</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46030</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22427,7 +22427,7 @@
         <v>45169</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22505,7 +22505,7 @@
         <v>46174</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>44979</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22656,7 +22656,7 @@
         <v>46036</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>45169</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22812,7 +22812,7 @@
         <v>44956</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>44824</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22963,7 +22963,7 @@
         <v>46029</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23036,7 +23036,7 @@
         <v>46038</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23114,7 +23114,7 @@
         <v>46174</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23192,7 +23192,7 @@
         <v>46043</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23270,7 +23270,7 @@
         <v>46042</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44910</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45471</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>45551</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>45055</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23655,7 +23655,7 @@
         <v>46042</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23733,7 +23733,7 @@
         <v>46174</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>46042</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>45169</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46010</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45315</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>46091</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>46036</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>46051</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>46051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>46176</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45771</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46055</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>46178</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>46054</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44958</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46059</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>44557</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>46099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25102,7 +25102,7 @@
         <v>45246</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>46059</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>46063</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>45565</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45239</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>46181</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>46182</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>46182</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>46072</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45562</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25872,7 +25872,7 @@
         <v>45223</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>46086</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26028,7 +26028,7 @@
         <v>46085</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45202</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45448</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45036</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>46185</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26413,7 +26413,7 @@
         <v>45565</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45852</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26569,7 +26569,7 @@
         <v>45852</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26647,7 +26647,7 @@
         <v>45755</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26720,7 +26720,7 @@
         <v>45796</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45244</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>45636</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>45448</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>46191</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>46099</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>46195</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>46195</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>46196</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27412,7 +27412,7 @@
         <v>46104</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>46198</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27563,7 +27563,7 @@
         <v>45735</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46107</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45566</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>44942</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>46198</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45632</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>46111</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>46198</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>46111</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28255,7 +28255,7 @@
         <v>46111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28333,7 +28333,7 @@
         <v>46114</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>46113</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28489,7 +28489,7 @@
         <v>45519</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28562,7 +28562,7 @@
         <v>46120</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>46121</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28718,7 +28718,7 @@
         <v>46126</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28796,7 +28796,7 @@
         <v>46123</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28874,7 +28874,7 @@
         <v>46125</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>46126</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29030,7 +29030,7 @@
         <v>46125</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>46125</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>46204</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>46133</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>45393</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45253</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>46133</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>46133</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45846</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>45111</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45180</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>46136</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>46136</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>44888</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>45223</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>46247</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30248,7 +30248,7 @@
         <v>44956</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30326,7 +30326,7 @@
         <v>46209</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30399,7 +30399,7 @@
         <v>44481</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>46206</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30550,7 +30550,7 @@
         <v>46248</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30628,7 +30628,7 @@
         <v>45253</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30701,7 +30701,7 @@
         <v>45253</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30774,7 +30774,7 @@
         <v>46206</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30852,7 +30852,7 @@
         <v>45148</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30930,7 +30930,7 @@
         <v>45198</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31008,7 +31008,7 @@
         <v>46253</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31154,7 +31154,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>44484</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>46211</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45244</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31529,7 +31529,7 @@
         <v>46212</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46254</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31680,7 +31680,7 @@
         <v>46212</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31753,7 +31753,7 @@
         <v>46212</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>44494</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>45103</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31977,7 +31977,7 @@
         <v>46211</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>46213</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32128,7 +32128,7 @@
         <v>46213</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>44848</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46218</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32352,7 +32352,7 @@
         <v>45385</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46218</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46217</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45586</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32732,7 +32732,7 @@
         <v>46261</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46217</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32883,7 +32883,7 @@
         <v>46218</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>46261</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33039,7 +33039,7 @@
         <v>46261</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33112,7 +33112,7 @@
         <v>46261</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>45075</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33268,7 +33268,7 @@
         <v>44748</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45488</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33424,7 +33424,7 @@
         <v>46220</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>45182</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>46262</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>45734</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33726,7 +33726,7 @@
         <v>46224</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46224</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>46224</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>46268</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45572</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34111,7 +34111,7 @@
         <v>45478</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>45614</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34257,7 +34257,7 @@
         <v>45562</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>46279</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>45789</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34491,7 +34491,7 @@
         <v>46281</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>44645</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45771</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45140</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45485</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45792</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>45551</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35017,7 +35017,7 @@
         <v>46282</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35095,7 +35095,7 @@
         <v>45517</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45614</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>45803</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>45800</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35397,7 +35397,7 @@
         <v>45805</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35475,7 +35475,7 @@
         <v>45807</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45807</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45664</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45742</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35777,7 +35777,7 @@
         <v>45811</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>45817</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35933,7 +35933,7 @@
         <v>45824</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36006,7 +36006,7 @@
         <v>45833</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>45833</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45847</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45846</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45848</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36381,7 +36381,7 @@
         <v>45849</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45852</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>45855</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45855</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45855</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45855</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>45866</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45866</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45874</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45874</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45875</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>45876</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45877</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>45876</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37448,7 +37448,7 @@
         <v>45882</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45882</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45882</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45882</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45883</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45883</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45882</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45712</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45506</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45749</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45733</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45858</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>45876</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38427,7 +38427,7 @@
         <v>45889</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>46189</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38583,7 +38583,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46198</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45202</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45820</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>46047</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>44902</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>46261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>46240</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44855</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45898</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45945</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>45057</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44994</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46209</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44878</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>46261</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>45302</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46238</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44606</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>46240</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44509</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44629</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44845</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44851</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>44465</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45471</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45734</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45228</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45228</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45393</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44761</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45198</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45399</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45224</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44974</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44956</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>46017</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45448</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45520</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45517</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44582</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45244</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45253</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44860</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45483</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45883</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>46036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45800</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45891</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>46038</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>46042</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44484</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>46043</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45898</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>46036</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45903</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>46091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45905</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>46051</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46051</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>46055</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44889</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>46054</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45912</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45912</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44557</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45915</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44925</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45803</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>45845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44974</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45845</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>46072</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45565</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44971</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45807</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45664</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45936</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46085</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>46086</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44956</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45071</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45755</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45852</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45852</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45448</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44958</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45811</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45539</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46104</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45461</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>46107</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45954</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>46111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>46111</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46113</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46121</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46120</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44956</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46125</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>46123</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>46125</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>46125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45966</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46126</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45519</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45642</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46126</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45975</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45975</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45977</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45980</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45982</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46133</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46133</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45982</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45642</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45986</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45988</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45988</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45182</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45862</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45846</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45149</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>46140</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45996</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45198</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44494</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45636</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>46010</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45978</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46003</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46136</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>46003</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>46007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>46007</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46007</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>44888</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46009</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>46136</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45611</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45013</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45988</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45705</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45876</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44889</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45351</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46136</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46139</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>46136</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45678</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>46141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46136</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>46136</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>46146</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46147</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>46149</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46150</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46150</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46189</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46189</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46189</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46153</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>44888</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46153</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44568</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>44960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45747</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45833</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>46155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46160</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45757</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45036</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45882</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45505</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45561</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45491</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>45962</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45846</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46162</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45848</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45847</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45849</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45852</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45855</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45855</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45855</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44979</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45866</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45866</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46174</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46099</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45098</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>46178</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45556</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46182</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45586</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>46185</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45180</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45874</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45721</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45876</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46191</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45875</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45876</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45331</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46195</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46195</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45075</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45148</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45614</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45877</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45712</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45882</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45882</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45882</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46204</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46248</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45672</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46209</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>46206</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>46253</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>46212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>46212</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>46213</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>46254</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46213</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46217</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44742</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>46218</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>46218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>46261</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>46261</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46261</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>46261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>46261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46262</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46218</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45169</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46220</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45735</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45771</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46224</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>46224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>46224</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44748</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46279</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45246</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>46281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44481</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45642</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45392</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45547</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44848</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45565</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46287</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45586</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46247</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>44980</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45562</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45097</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44942</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45566</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45639</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45036</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45448</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45356</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45351</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45253</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45253</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45055</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44524</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45516</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>44889</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45125</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45217</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44876</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>45735</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45223</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45446</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45642</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45713</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45257</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45315</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45253</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45471</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45103</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45572</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45478</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45614</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45562</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45789</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45771</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45792</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45485</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44645</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45140</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45506</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45749</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45733</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45858</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45876</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45889</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>46189</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46198</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45202</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45820</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         <v>45063</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>46047</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>44902</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         <v>45840</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>46261</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45471</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>44603</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>46240</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>44855</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>45898</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45807</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45945</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5066,7 +5066,7 @@
         <v>45057</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5281,7 +5281,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46150</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>44994</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5606,7 +5606,7 @@
         <v>46181</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>45629</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46209</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>44878</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>45198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
         <v>46261</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6265,7 +6265,7 @@
         <v>45302</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6375,7 +6375,7 @@
         <v>46238</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44606</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>45756</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6815,7 +6815,7 @@
         <v>46240</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44509</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44810</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
         <v>44629</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44834</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44725</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7410,7 +7410,7 @@
         <v>44859</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44845</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>44851</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>44587</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>44465</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         <v>45471</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>45734</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7946,7 +7946,7 @@
         <v>45330</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8019,7 +8019,7 @@
         <v>45228</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>45228</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>45393</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8238,7 +8238,7 @@
         <v>44761</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>45198</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8389,7 +8389,7 @@
         <v>45399</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         <v>45224</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44910</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44824</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>44974</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45551</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44956</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>46017</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
         <v>45448</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9144,7 +9144,7 @@
         <v>45520</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>45551</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>45517</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>44582</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9441,7 +9441,7 @@
         <v>45140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>45140</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9670,7 +9670,7 @@
         <v>45244</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9748,7 +9748,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9821,7 +9821,7 @@
         <v>45253</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44860</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>45488</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>45483</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45883</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10211,7 +10211,7 @@
         <v>45883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>45169</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10367,7 +10367,7 @@
         <v>46036</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
         <v>45800</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10523,7 +10523,7 @@
         <v>45891</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10601,7 +10601,7 @@
         <v>45893</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>46038</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>46042</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44484</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>46029</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11137,7 +11137,7 @@
         <v>46043</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45898</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>46010</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>46036</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45622</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11517,7 +11517,7 @@
         <v>45904</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11595,7 +11595,7 @@
         <v>45903</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11673,7 +11673,7 @@
         <v>46091</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>45905</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>46051</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>46051</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>46055</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>44889</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>46054</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45912</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>45912</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45916</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>44557</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45915</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44925</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>45915</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>45916</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45917</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>46059</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>46059</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45917</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13208,7 +13208,7 @@
         <v>45803</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13286,7 +13286,7 @@
         <v>45917</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>46063</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13442,7 +13442,7 @@
         <v>45491</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>45845</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44974</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45845</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>46072</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45805</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45565</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>44971</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>45807</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>45664</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45936</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14426,7 +14426,7 @@
         <v>45936</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>46085</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14577,7 +14577,7 @@
         <v>46086</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14655,7 +14655,7 @@
         <v>45936</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>44956</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44719</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14962,7 +14962,7 @@
         <v>45742</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>45796</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15113,7 +15113,7 @@
         <v>45937</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>45071</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>45755</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45852</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45852</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45448</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15571,7 +15571,7 @@
         <v>46099</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15644,7 +15644,7 @@
         <v>44958</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>45811</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45574</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45463</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45539</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46104</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>45461</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>46107</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>45954</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>46111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>46111</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>46111</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46113</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>46114</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45959</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>46121</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46120</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>44956</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45965</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>46125</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>46123</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>46125</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>46125</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45966</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46126</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>45519</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45642</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         <v>46126</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17886,7 +17886,7 @@
         <v>45817</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45975</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45975</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45978</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45978</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45977</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45980</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45980</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>45982</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45981</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>45981</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>46133</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>46133</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>46133</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45982</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
         <v>45642</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>45125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>46136</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19338,7 +19338,7 @@
         <v>45986</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19411,7 +19411,7 @@
         <v>45988</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45988</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19557,7 +19557,7 @@
         <v>45988</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19630,7 +19630,7 @@
         <v>45182</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19781,7 +19781,7 @@
         <v>45862</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45846</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45149</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>46140</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>45169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45996</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>45198</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45170</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20453,7 +20453,7 @@
         <v>44494</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20526,7 +20526,7 @@
         <v>45866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20604,7 +20604,7 @@
         <v>45295</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45636</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20755,7 +20755,7 @@
         <v>46010</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20828,7 +20828,7 @@
         <v>45978</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20901,7 +20901,7 @@
         <v>46003</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>46136</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21047,7 +21047,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21120,7 +21120,7 @@
         <v>46003</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21198,7 +21198,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>46013</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21349,7 +21349,7 @@
         <v>45539</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21427,7 +21427,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21505,7 +21505,7 @@
         <v>46007</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>46007</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21651,7 +21651,7 @@
         <v>46007</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21724,7 +21724,7 @@
         <v>45755</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45614</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21870,7 +21870,7 @@
         <v>46007</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21943,7 +21943,7 @@
         <v>44888</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>46009</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22094,7 +22094,7 @@
         <v>46010</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22167,7 +22167,7 @@
         <v>46136</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22240,7 +22240,7 @@
         <v>45611</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>45824</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45013</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>45988</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>45705</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22605,7 +22605,7 @@
         <v>45876</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>44889</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45351</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22834,7 +22834,7 @@
         <v>46136</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>46139</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>46136</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45678</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>46141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>46136</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>45111</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23506,7 +23506,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23584,7 +23584,7 @@
         <v>46136</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>46146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23735,7 +23735,7 @@
         <v>46146</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23813,7 +23813,7 @@
         <v>46147</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>46147</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23969,7 +23969,7 @@
         <v>46149</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24047,7 +24047,7 @@
         <v>46150</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24125,7 +24125,7 @@
         <v>46150</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>46189</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24276,7 +24276,7 @@
         <v>46189</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24349,7 +24349,7 @@
         <v>46189</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24422,7 +24422,7 @@
         <v>46153</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24500,7 +24500,7 @@
         <v>44888</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24573,7 +24573,7 @@
         <v>46153</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24651,7 +24651,7 @@
         <v>44568</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24724,7 +24724,7 @@
         <v>44960</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>45747</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24943,7 +24943,7 @@
         <v>45833</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>46155</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>46107</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>46160</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25250,7 +25250,7 @@
         <v>45161</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>45757</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45036</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45882</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45505</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>46162</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>46162</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45561</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25864,7 +25864,7 @@
         <v>45239</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45069</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45491</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26093,7 +26093,7 @@
         <v>45962</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45846</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26239,7 +26239,7 @@
         <v>46162</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26317,7 +26317,7 @@
         <v>46162</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26390,7 +26390,7 @@
         <v>45848</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45847</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26546,7 +26546,7 @@
         <v>45849</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26624,7 +26624,7 @@
         <v>45852</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45600</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45855</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45855</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45855</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45855</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44979</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27223,7 +27223,7 @@
         <v>45866</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45866</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27379,7 +27379,7 @@
         <v>44979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>46174</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>46099</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27759,7 +27759,7 @@
         <v>46181</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27837,7 +27837,7 @@
         <v>45098</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         <v>46178</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27988,7 +27988,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28061,7 +28061,7 @@
         <v>45556</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>46182</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28212,7 +28212,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>45586</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>46185</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28446,7 +28446,7 @@
         <v>45180</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45874</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45721</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45876</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>46191</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45875</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>45876</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28982,7 +28982,7 @@
         <v>45331</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29055,7 +29055,7 @@
         <v>46195</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46195</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29211,7 +29211,7 @@
         <v>45075</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29362,7 +29362,7 @@
         <v>46196</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45148</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45614</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29591,7 +29591,7 @@
         <v>46198</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>46198</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45877</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29903,7 +29903,7 @@
         <v>45712</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45882</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30054,7 +30054,7 @@
         <v>45882</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>45882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         <v>45882</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30273,7 +30273,7 @@
         <v>45882</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>46204</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30424,7 +30424,7 @@
         <v>46248</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30502,7 +30502,7 @@
         <v>45672</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30580,7 +30580,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30658,7 +30658,7 @@
         <v>46209</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>46206</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>46253</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30882,7 +30882,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>46211</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>46253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>46253</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31184,7 +31184,7 @@
         <v>46253</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>46212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>46212</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31403,7 +31403,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>46213</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31554,7 +31554,7 @@
         <v>46254</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>46213</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31705,7 +31705,7 @@
         <v>46217</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44742</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31856,7 +31856,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31934,7 +31934,7 @@
         <v>46217</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>46218</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32090,7 +32090,7 @@
         <v>46218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32168,7 +32168,7 @@
         <v>46261</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32241,7 +32241,7 @@
         <v>46261</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32319,7 +32319,7 @@
         <v>46261</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32392,7 +32392,7 @@
         <v>46261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>46261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32543,7 +32543,7 @@
         <v>46262</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32616,7 +32616,7 @@
         <v>46218</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32694,7 +32694,7 @@
         <v>45169</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32772,7 +32772,7 @@
         <v>46220</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32850,7 +32850,7 @@
         <v>45735</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45771</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>46224</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33084,7 +33084,7 @@
         <v>46268</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>46224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33235,7 +33235,7 @@
         <v>46224</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>44748</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45202</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>44974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46279</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45246</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>46281</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44481</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46282</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45642</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45392</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>45547</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34156,7 +34156,7 @@
         <v>44848</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45565</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46287</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34380,7 +34380,7 @@
         <v>45586</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>46247</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>44980</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34604,7 +34604,7 @@
         <v>45562</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45097</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>44942</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34828,7 +34828,7 @@
         <v>45566</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45639</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45036</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45448</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45356</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45770</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35281,7 +35281,7 @@
         <v>45351</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45253</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45253</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45055</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>44524</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45516</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>44889</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45125</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45142</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45217</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>44876</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>45735</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36177,7 +36177,7 @@
         <v>45223</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45446</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45642</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>45713</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36484,7 +36484,7 @@
         <v>45257</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36562,7 +36562,7 @@
         <v>45315</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45720</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45253</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45471</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>45103</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45572</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45478</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37093,7 +37093,7 @@
         <v>45614</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37166,7 +37166,7 @@
         <v>45562</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37244,7 +37244,7 @@
         <v>45789</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45771</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45792</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>45485</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44645</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45140</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>45506</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45749</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>45733</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37926,7 +37926,7 @@
         <v>45858</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45876</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45889</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46279</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38233,7 +38233,7 @@
         <v>46189</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46212</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>44853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46198</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45202</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45820</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44957</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>46047</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45418</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45553</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46296</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44878</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44855</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45302</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44994</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>46209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>46261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46238</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45057</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46240</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>45170</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45330</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45721</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45556</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45036</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44876</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>46007</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>46007</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>46007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45755</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44645</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>46009</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>46010</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45446</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46017</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45891</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>46030</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45125</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45898</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45903</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45485</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46029</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45904</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46038</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46043</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45551</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>46042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45915</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>46010</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45912</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45912</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45917</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46091</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45916</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45917</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>46051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>46051</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45800</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45807</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45807</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>46055</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45845</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>46059</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>46063</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45735</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45936</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45461</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45936</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45351</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>46072</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45811</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45539</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45574</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45228</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45228</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46086</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44582</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45852</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45755</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45796</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45966</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45586</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>46099</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45720</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45975</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46104</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>46107</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45356</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45982</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>46111</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45471</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>46111</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46114</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>46113</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45988</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45824</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45988</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>46120</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45988</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46121</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45331</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46126</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45862</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46123</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>46126</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46125</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46125</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45996</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>46133</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46133</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45833</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45833</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45846</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46136</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45142</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45757</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45098</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45351</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45846</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45848</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45849</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>46136</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45852</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45770</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45855</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45855</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45639</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45672</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45978</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45642</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45855</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44971</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>46136</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45611</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45720</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46136</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45295</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46141</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45876</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45866</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44925</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45866</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46136</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45069</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45614</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45614</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>46136</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45678</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45866</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45224</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45713</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45217</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46146</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>46147</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44956</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46189</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>46189</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>46149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>46150</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>46150</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>46153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>46155</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45561</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45642</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45642</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44960</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45882</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46107</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45505</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45874</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>46160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45491</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45875</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45962</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>46162</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45876</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46162</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45877</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44568</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46162</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45600</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45882</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45516</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45882</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45883</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45475</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45882</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45712</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45448</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45071</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45399</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44889</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46182</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44524</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46185</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46191</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45552</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45149</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44979</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46195</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>46196</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44761</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>46204</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45392</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44719</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44956</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46212</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44910</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45471</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45551</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45055</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>46211</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45169</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45315</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46213</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46213</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45771</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>46218</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>46261</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>46217</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>46261</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46217</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46218</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46261</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46261</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46220</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46262</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44557</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45246</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45565</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>46224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45239</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46224</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46268</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45562</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45223</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46279</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45448</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46281</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45036</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45565</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46282</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45244</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45636</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45448</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45735</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45566</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44942</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45632</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46287</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45519</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>46265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>46247</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45393</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45253</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45520</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45180</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>46295</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45223</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44956</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>44481</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46253</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46253</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>46254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46253</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46253</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45148</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45198</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>44484</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45244</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44494</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45103</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44848</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45385</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45586</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45075</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>44748</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45488</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45734</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45572</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45478</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45614</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45562</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45506</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45749</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45733</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45858</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45876</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45889</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>46279</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46189</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>46212</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         <v>44853</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         <v>45225</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>46198</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45202</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45820</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45981</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>44957</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>46047</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
         <v>45418</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45937</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>44902</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45471</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45553</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3972,7 +3972,7 @@
         <v>45840</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4083,7 +4083,7 @@
         <v>45429</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>46296</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44878</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45890</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4961,7 +4961,7 @@
         <v>45807</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45945</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>44855</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45534</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45110</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         <v>45302</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>46150</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>44994</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>46181</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>46209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>46261</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>45629</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46238</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>45057</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45629</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45198</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>46258</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46240</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>45170</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>45330</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>45721</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>45556</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45257</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>45036</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>45789</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>46003</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         <v>44876</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8656,7 +8656,7 @@
         <v>45097</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>46003</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>46007</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>46007</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>46007</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>45755</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44645</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
         <v>46007</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         <v>46009</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45539</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45771</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>46010</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9547,7 +9547,7 @@
         <v>45446</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45125</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>45491</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>46017</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45891</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9932,7 +9932,7 @@
         <v>45893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         <v>46030</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45125</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>45898</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         <v>44889</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10307,7 +10307,7 @@
         <v>46036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10385,7 +10385,7 @@
         <v>45903</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45485</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45905</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>46029</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45904</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>46038</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10916,7 +10916,7 @@
         <v>46043</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>46042</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45140</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45792</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>46042</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45551</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>46042</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45517</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>45614</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45912</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>45915</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>46010</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11832,7 +11832,7 @@
         <v>45915</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11910,7 +11910,7 @@
         <v>45912</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11988,7 +11988,7 @@
         <v>45912</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>45917</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>46091</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>45916</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>45916</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12378,7 +12378,7 @@
         <v>45917</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12456,7 +12456,7 @@
         <v>46036</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12529,7 +12529,7 @@
         <v>46051</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>46051</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45803</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45800</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45805</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45807</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>45845</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45807</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>46055</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45845</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13377,7 +13377,7 @@
         <v>46054</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13455,7 +13455,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>46059</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>46063</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45547</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>45735</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>45936</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13976,7 +13976,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14054,7 +14054,7 @@
         <v>45664</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14127,7 +14127,7 @@
         <v>45742</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>45461</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>45936</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45036</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45938</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>45351</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14663,7 +14663,7 @@
         <v>46072</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14736,7 +14736,7 @@
         <v>45811</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>45539</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14892,7 +14892,7 @@
         <v>45198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14970,7 +14970,7 @@
         <v>45574</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45463</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45228</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45228</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>46086</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45954</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45959</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44582</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15662,7 +15662,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15740,7 +15740,7 @@
         <v>45817</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15818,7 +15818,7 @@
         <v>45852</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15896,7 +15896,7 @@
         <v>45852</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45755</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45796</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16125,7 +16125,7 @@
         <v>45966</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16203,7 +16203,7 @@
         <v>45966</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>45586</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>45013</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>46099</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>44742</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>45720</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45975</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45975</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>46104</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45977</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45978</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45978</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>46107</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>45980</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>45980</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45980</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>45981</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45981</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17572,7 +17572,7 @@
         <v>45356</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45982</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17723,7 +17723,7 @@
         <v>46111</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>46111</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45471</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>46111</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>45982</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>46114</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18191,7 +18191,7 @@
         <v>45986</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18264,7 +18264,7 @@
         <v>46113</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45988</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45824</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45988</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>46120</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45988</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>46121</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45331</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44889</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>46126</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45862</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>46123</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>46125</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19243,7 +19243,7 @@
         <v>46126</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19321,7 +19321,7 @@
         <v>46125</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19399,7 +19399,7 @@
         <v>46125</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>45996</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46133</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45140</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19706,7 +19706,7 @@
         <v>46133</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>46133</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45833</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45833</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45846</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46136</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>46136</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45142</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20300,7 +20300,7 @@
         <v>44888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>45483</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45757</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45098</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>45705</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45351</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20831,7 +20831,7 @@
         <v>45847</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45846</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>45848</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21060,7 +21060,7 @@
         <v>46136</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21133,7 +21133,7 @@
         <v>45849</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21211,7 +21211,7 @@
         <v>46136</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>44974</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45852</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45770</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45855</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>45855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45855</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45855</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46010</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45639</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45672</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45253</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45978</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>45988</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45642</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45855</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44971</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22477,7 +22477,7 @@
         <v>46136</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45611</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45720</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>46136</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45295</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46141</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22925,7 +22925,7 @@
         <v>45876</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45866</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>44925</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45866</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>46136</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
         <v>46141</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>46140</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45069</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46141</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45614</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45614</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>46136</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45678</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>45866</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45224</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45713</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>45217</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24347,7 +24347,7 @@
         <v>44974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24420,7 +24420,7 @@
         <v>46146</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>46147</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>46146</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>46147</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24732,7 +24732,7 @@
         <v>44956</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>46189</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>46189</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25029,7 +25029,7 @@
         <v>46149</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25107,7 +25107,7 @@
         <v>45747</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25180,7 +25180,7 @@
         <v>45874</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25253,7 +25253,7 @@
         <v>46150</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25331,7 +25331,7 @@
         <v>46153</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>46150</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25487,7 +25487,7 @@
         <v>46153</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25565,7 +25565,7 @@
         <v>46155</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45561</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>44888</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25794,7 +25794,7 @@
         <v>45642</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25867,7 +25867,7 @@
         <v>45642</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44960</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26018,7 +26018,7 @@
         <v>45882</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26091,7 +26091,7 @@
         <v>46107</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26247,7 +26247,7 @@
         <v>45505</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26325,7 +26325,7 @@
         <v>45874</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26398,7 +26398,7 @@
         <v>46160</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45491</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45875</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         <v>45962</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26705,7 +26705,7 @@
         <v>46162</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45876</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>46162</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45877</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27012,7 +27012,7 @@
         <v>44568</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27085,7 +27085,7 @@
         <v>46162</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>46162</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27241,7 +27241,7 @@
         <v>45600</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27314,7 +27314,7 @@
         <v>45876</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44979</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45882</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>46174</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45516</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46174</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44980</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>45882</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>45882</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27991,7 +27991,7 @@
         <v>45882</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45883</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45475</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45882</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45712</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28371,7 +28371,7 @@
         <v>46178</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28449,7 +28449,7 @@
         <v>45448</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45071</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46099</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>45399</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44889</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>46181</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28897,7 +28897,7 @@
         <v>46182</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>46182</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>44524</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46185</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46191</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>45552</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>45149</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>44979</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46195</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29667,7 +29667,7 @@
         <v>46196</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>44761</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29818,7 +29818,7 @@
         <v>46198</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>45036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29969,7 +29969,7 @@
         <v>46198</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>46198</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>46204</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45392</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>44719</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>46209</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>46206</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>46206</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30666,7 +30666,7 @@
         <v>45169</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>44956</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30817,7 +30817,7 @@
         <v>44824</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30895,7 +30895,7 @@
         <v>46211</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46212</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>44910</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45471</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31202,7 +31202,7 @@
         <v>45551</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>46212</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31348,7 +31348,7 @@
         <v>45055</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>46212</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31504,7 +31504,7 @@
         <v>46211</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31582,7 +31582,7 @@
         <v>45169</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31660,7 +31660,7 @@
         <v>45315</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>46213</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31811,7 +31811,7 @@
         <v>46213</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45771</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31962,7 +31962,7 @@
         <v>46218</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32040,7 +32040,7 @@
         <v>46261</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>46218</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>46217</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>46261</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32342,7 +32342,7 @@
         <v>46217</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32420,7 +32420,7 @@
         <v>46218</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>46261</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32649,7 +32649,7 @@
         <v>46261</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32727,7 +32727,7 @@
         <v>46220</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>46262</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32878,7 +32878,7 @@
         <v>44958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>44557</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33024,7 +33024,7 @@
         <v>45246</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33102,7 +33102,7 @@
         <v>45565</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33180,7 +33180,7 @@
         <v>46224</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33258,7 +33258,7 @@
         <v>45239</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33336,7 +33336,7 @@
         <v>46224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33414,7 +33414,7 @@
         <v>46224</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33492,7 +33492,7 @@
         <v>46268</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33565,7 +33565,7 @@
         <v>45562</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33643,7 +33643,7 @@
         <v>45223</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33721,7 +33721,7 @@
         <v>46279</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45202</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>45448</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33955,7 +33955,7 @@
         <v>46281</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34033,7 +34033,7 @@
         <v>45036</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         <v>45565</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34184,7 +34184,7 @@
         <v>46282</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34262,7 +34262,7 @@
         <v>45244</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34340,7 +34340,7 @@
         <v>45636</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34418,7 +34418,7 @@
         <v>45448</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45735</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34574,7 +34574,7 @@
         <v>45566</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34647,7 +34647,7 @@
         <v>44942</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34720,7 +34720,7 @@
         <v>45632</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34798,7 +34798,7 @@
         <v>46287</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34871,7 +34871,7 @@
         <v>45519</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34944,7 +34944,7 @@
         <v>46265</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35022,7 +35022,7 @@
         <v>46265</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35100,7 +35100,7 @@
         <v>46248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35178,7 +35178,7 @@
         <v>46293</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35256,7 +35256,7 @@
         <v>46247</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35329,7 +35329,7 @@
         <v>45393</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35402,7 +35402,7 @@
         <v>45253</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45520</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35553,7 +35553,7 @@
         <v>45111</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35631,7 +35631,7 @@
         <v>45180</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>46295</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>45223</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35865,7 +35865,7 @@
         <v>44956</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35943,7 +35943,7 @@
         <v>44481</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>46253</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36089,7 +36089,7 @@
         <v>46253</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36162,7 +36162,7 @@
         <v>46254</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36240,7 +36240,7 @@
         <v>46253</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46253</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>45253</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45253</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36532,7 +36532,7 @@
         <v>45148</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>45198</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>44484</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45244</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>44494</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36912,7 +36912,7 @@
         <v>45103</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36985,7 +36985,7 @@
         <v>44848</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37058,7 +37058,7 @@
         <v>45385</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45586</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45075</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>44748</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45488</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45182</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45734</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37594,7 +37594,7 @@
         <v>45572</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45478</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>45614</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45562</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37896,7 +37896,7 @@
         <v>45506</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37974,7 +37974,7 @@
         <v>45749</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45733</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45858</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45876</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45889</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
         <v>46279</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46189</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45629</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45428</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45119</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45356</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45063</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45820</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45429</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>46047</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45471</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>46261</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44855</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>45629</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45807</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44878</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45945</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45302</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45534</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46209</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>46261</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>46240</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>45471</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>45253</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45253</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44568</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44524</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45399</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45516</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45734</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45330</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45757</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45036</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>45142</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>45228</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45228</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45069</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45224</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44824</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44956</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45883</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45448</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>44582</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45140</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45140</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45446</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45713</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45253</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44860</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45257</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45488</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45483</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45891</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45893</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45315</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44484</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45905</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45471</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45103</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45036</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45912</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45912</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45572</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45478</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45556</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45614</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45915</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45916</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>44889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45586</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44557</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45180</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45562</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45491</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45721</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45845</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45771</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45331</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45792</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45485</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45075</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45565</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45140</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45552</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45517</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45614</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44956</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45448</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45672</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45805</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45807</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45807</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45742</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45811</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45463</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44956</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44742</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45519</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45642</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45954</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45959</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45223</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45966</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45642</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45125</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45846</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45182</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45848</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45847</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45632</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45849</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45852</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45735</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45149</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45855</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45169</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45855</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45855</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45170</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44494</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45771</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45866</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45975</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>44748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45978</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45977</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45874</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45475</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45980</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45980</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>44974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45876</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45876</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45982</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>45877</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45882</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45882</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44889</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45982</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45246</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44481</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45988</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46111</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45392</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46113</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>46114</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45547</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45862</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>46121</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>46120</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46125</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46123</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>46125</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>44848</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46125</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>46126</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45565</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>46133</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>46003</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46133</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46133</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46003</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45586</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46136</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46007</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45846</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46140</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46017</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45855</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45562</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45866</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>46030</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45295</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46010</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>46136</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46136</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>46013</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45566</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45614</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46136</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46042</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46042</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46042</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>46029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45611</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>46043</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45639</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45988</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45036</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45448</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45705</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45876</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45351</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45356</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46139</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46010</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45770</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45351</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46136</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45678</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>46091</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>46141</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46141</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>46051</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46051</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>46055</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>46054</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46136</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>46141</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>46059</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>46059</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>46146</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46063</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>46146</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>46147</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46147</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>46149</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>46150</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46150</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>46189</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46189</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46189</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>46153</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>46072</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44888</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>46153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44960</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>46155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46085</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46086</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45505</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46162</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45796</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45755</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45852</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45852</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45491</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45962</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46162</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>46162</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45600</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44979</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>46174</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>46099</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46185</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46191</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>46195</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46206</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46209</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46211</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46211</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46212</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>46212</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>46212</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>46213</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46213</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46217</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>46217</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46218</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>46218</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46218</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>46268</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>46224</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46224</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46282</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46287</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>46293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45520</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>46248</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46253</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46253</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46295</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46254</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>46300</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>46261</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>46261</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46304</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46261</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>46304</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>46261</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46261</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46304</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45506</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45749</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45733</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45858</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45876</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45889</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46189</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45412</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45813</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45629</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
         <v>45428</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45119</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1707,7 +1707,7 @@
         <v>45356</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>44526</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45063</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45820</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45553</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>45418</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45840</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3862,7 +3862,7 @@
         <v>45429</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>46047</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>45471</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>46296</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>46261</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44855</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>45898</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44994</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5067,7 +5067,7 @@
         <v>45629</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45807</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>44878</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45057</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45945</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>45198</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
         <v>45302</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5831,7 +5831,7 @@
         <v>45110</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>45534</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>46181</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46209</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>46238</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>46261</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44606</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>45756</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>46240</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46258</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7219,7 +7219,7 @@
         <v>44810</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7297,7 +7297,7 @@
         <v>44629</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         <v>44834</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         <v>44725</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44859</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>44845</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>44851</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>44587</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         <v>44761</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>45198</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
         <v>45471</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>45253</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45253</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44568</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>45055</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44524</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>45399</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>45385</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>45516</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44889</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>45734</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>45330</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>45757</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45036</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>45125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>45142</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>45228</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45228</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9318,7 +9318,7 @@
         <v>45561</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>45239</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44910</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>45069</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>45224</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>45217</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44824</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>44876</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45735</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44974</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45551</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>45223</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44956</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>45883</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45448</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>44582</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45140</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10687,7 +10687,7 @@
         <v>45140</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10765,7 +10765,7 @@
         <v>44979</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>45446</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>45244</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10999,7 +10999,7 @@
         <v>45642</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11072,7 +11072,7 @@
         <v>45713</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>45253</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44860</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>45257</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45488</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         <v>45483</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11540,7 +11540,7 @@
         <v>45891</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>45893</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>45898</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45315</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45720</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45169</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12008,7 +12008,7 @@
         <v>45253</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45904</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45903</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44484</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>45905</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45471</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         <v>45103</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12539,7 +12539,7 @@
         <v>45036</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12612,7 +12612,7 @@
         <v>45098</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12685,7 +12685,7 @@
         <v>45912</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>45622</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>45912</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12919,7 +12919,7 @@
         <v>45572</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12997,7 +12997,7 @@
         <v>45478</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13070,7 +13070,7 @@
         <v>45912</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13148,7 +13148,7 @@
         <v>45916</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>45556</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13299,7 +13299,7 @@
         <v>45614</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>45915</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>45916</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>44889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13679,7 +13679,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>45586</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>44557</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>44925</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45180</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>45562</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14293,7 +14293,7 @@
         <v>45491</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>45721</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14522,7 +14522,7 @@
         <v>45845</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14595,7 +14595,7 @@
         <v>45789</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14673,7 +14673,7 @@
         <v>44974</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>45771</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45331</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14897,7 +14897,7 @@
         <v>45792</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45485</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>44645</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45075</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45565</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45140</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45036</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45552</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>44971</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45148</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45551</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45517</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45614</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45614</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44956</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45936</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44719</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>45800</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45071</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>45448</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>45672</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45803</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>44958</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>45805</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>45938</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16938,7 +16938,7 @@
         <v>45807</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45807</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45742</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45811</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45461</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45574</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>45463</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45539</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>45817</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>44956</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>45824</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44742</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45519</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45642</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45954</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>45959</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>45223</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>45833</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45833</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45966</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45966</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45642</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45125</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>45169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45846</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19067,7 +19067,7 @@
         <v>45182</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45848</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45847</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45632</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45849</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45852</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45735</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>45149</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45855</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19759,7 +19759,7 @@
         <v>45169</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19837,7 +19837,7 @@
         <v>45855</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45975</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45855</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45855</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20134,7 +20134,7 @@
         <v>45198</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45170</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>44494</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45771</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>45866</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45866</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         <v>45975</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>44748</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>45978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>45978</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45636</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45202</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45977</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21128,7 +21128,7 @@
         <v>45874</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45720</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45475</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45980</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45980</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>44974</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45874</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45980</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45876</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21815,7 +21815,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21893,7 +21893,7 @@
         <v>45876</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45982</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22127,7 +22127,7 @@
         <v>45981</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>45013</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>45877</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
         <v>45712</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45882</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45882</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45882</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>45882</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45882</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>44889</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45982</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>46099</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45246</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46104</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45244</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45986</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>44481</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45988</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>46107</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>45988</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45988</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45111</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>46111</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23846,7 +23846,7 @@
         <v>45642</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>46111</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>46111</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24080,7 +24080,7 @@
         <v>45392</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>46113</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>46114</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24314,7 +24314,7 @@
         <v>45547</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45862</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24460,7 +24460,7 @@
         <v>46121</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24538,7 +24538,7 @@
         <v>46120</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>46125</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24694,7 +24694,7 @@
         <v>46123</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24772,7 +24772,7 @@
         <v>46125</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24850,7 +24850,7 @@
         <v>44848</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24923,7 +24923,7 @@
         <v>46125</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25001,7 +25001,7 @@
         <v>45996</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25074,7 +25074,7 @@
         <v>46126</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>45565</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25230,7 +25230,7 @@
         <v>46133</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>46003</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25381,7 +25381,7 @@
         <v>46133</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>46133</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>46003</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25615,7 +25615,7 @@
         <v>45586</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25693,7 +25693,7 @@
         <v>45539</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>46136</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>46007</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25917,7 +25917,7 @@
         <v>46007</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25990,7 +25990,7 @@
         <v>46007</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26063,7 +26063,7 @@
         <v>45755</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26136,7 +26136,7 @@
         <v>44980</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26209,7 +26209,7 @@
         <v>46007</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>46009</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45846</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46140</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26584,7 +26584,7 @@
         <v>46017</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45855</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45562</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26813,7 +26813,7 @@
         <v>45866</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26891,7 +26891,7 @@
         <v>46030</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45295</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>46010</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27183,7 +27183,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27256,7 +27256,7 @@
         <v>45978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>46136</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27402,7 +27402,7 @@
         <v>46136</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27475,7 +27475,7 @@
         <v>46013</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27548,7 +27548,7 @@
         <v>45566</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27621,7 +27621,7 @@
         <v>45614</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27694,7 +27694,7 @@
         <v>46036</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>44888</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27845,7 +27845,7 @@
         <v>46136</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>46038</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27996,7 +27996,7 @@
         <v>46042</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46042</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28152,7 +28152,7 @@
         <v>46042</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28230,7 +28230,7 @@
         <v>46029</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45611</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28376,7 +28376,7 @@
         <v>46043</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45639</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28532,7 +28532,7 @@
         <v>45988</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28605,7 +28605,7 @@
         <v>45036</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28678,7 +28678,7 @@
         <v>45448</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45705</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45876</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>45351</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>45356</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46136</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>46139</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>46010</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>46036</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29355,7 +29355,7 @@
         <v>45770</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45351</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29511,7 +29511,7 @@
         <v>46136</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29584,7 +29584,7 @@
         <v>45678</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29657,7 +29657,7 @@
         <v>46091</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>46141</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46141</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>46051</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46051</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>46055</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30115,7 +30115,7 @@
         <v>46054</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>46136</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30266,7 +30266,7 @@
         <v>46141</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30344,7 +30344,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30417,7 +30417,7 @@
         <v>46059</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30490,7 +30490,7 @@
         <v>46059</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30563,7 +30563,7 @@
         <v>46146</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30641,7 +30641,7 @@
         <v>46063</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>46146</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30797,7 +30797,7 @@
         <v>46147</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46147</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>46149</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>46150</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46150</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31187,7 +31187,7 @@
         <v>46189</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>46189</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31333,7 +31333,7 @@
         <v>46189</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31406,7 +31406,7 @@
         <v>46153</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>46072</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>44888</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>46153</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>44960</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>46155</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46085</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32010,7 +32010,7 @@
         <v>46086</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>46107</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45161</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45882</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32317,7 +32317,7 @@
         <v>45505</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>46162</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45796</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45755</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45852</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32702,7 +32702,7 @@
         <v>45852</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>46162</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45491</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32936,7 +32936,7 @@
         <v>45962</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>46162</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>46162</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>45600</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>44979</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33311,7 +33311,7 @@
         <v>46174</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>46174</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33467,7 +33467,7 @@
         <v>46099</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33540,7 +33540,7 @@
         <v>46181</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33618,7 +33618,7 @@
         <v>46178</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33696,7 +33696,7 @@
         <v>46182</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33774,7 +33774,7 @@
         <v>46182</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>46185</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33930,7 +33930,7 @@
         <v>46191</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34003,7 +34003,7 @@
         <v>46195</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34081,7 +34081,7 @@
         <v>46195</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46196</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>46198</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34315,7 +34315,7 @@
         <v>46198</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34393,7 +34393,7 @@
         <v>46198</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46204</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46206</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46209</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34700,7 +34700,7 @@
         <v>46206</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>46211</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>46211</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46212</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>46212</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>46212</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35158,7 +35158,7 @@
         <v>46213</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46213</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46217</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35382,7 +35382,7 @@
         <v>46217</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35460,7 +35460,7 @@
         <v>46218</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>46218</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>46218</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>46220</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>46224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         <v>46268</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>46224</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>46224</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36079,7 +36079,7 @@
         <v>46279</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>46281</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36235,7 +36235,7 @@
         <v>46282</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36313,7 +36313,7 @@
         <v>46287</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36386,7 +36386,7 @@
         <v>46247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>46293</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36537,7 +36537,7 @@
         <v>46265</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45520</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>46248</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>46265</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46253</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>46253</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>46253</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>46295</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37141,7 +37141,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37214,7 +37214,7 @@
         <v>46300</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>46254</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37370,7 +37370,7 @@
         <v>46300</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>46261</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>46261</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>46304</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37662,7 +37662,7 @@
         <v>46261</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37735,7 +37735,7 @@
         <v>46304</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>46261</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37886,7 +37886,7 @@
         <v>46261</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>46262</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>46304</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>45506</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38188,7 +38188,7 @@
         <v>45749</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45733</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>45858</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38412,7 +38412,7 @@
         <v>45876</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38490,7 +38490,7 @@
         <v>45889</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46279</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38646,7 +38646,7 @@
         <v>46189</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45813</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45412</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45820</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45471</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45553</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45429</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>46047</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45418</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44878</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44855</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45534</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46150</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45302</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45945</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>46209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46238</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45198</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45807</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45057</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>46308</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46240</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>46258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44629</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44834</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44845</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44851</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45170</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45556</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45330</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45721</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45257</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45036</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45491</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45446</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45125</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44876</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44860</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>45547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45351</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45198</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45228</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45228</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45013</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45586</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45356</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45471</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45882</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45883</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45705</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45351</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>46136</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45331</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45891</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45988</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45893</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45140</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45855</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46136</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45611</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>46136</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45876</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46136</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45898</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46141</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45903</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45614</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46013</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46136</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45912</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45915</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45912</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45916</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45483</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45757</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45917</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46147</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46147</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45845</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>46189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>46189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45770</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>46189</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45747</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>46150</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>46153</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>46150</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46153</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45938</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45937</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45639</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45672</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44971</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45539</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45463</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45720</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>44888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44925</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45959</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>46107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45161</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45069</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45505</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45614</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45965</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45713</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45966</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45966</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45962</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45217</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>44974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45975</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44956</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45978</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46162</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>46162</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45980</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45980</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45981</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45981</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45600</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45982</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45561</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45982</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45988</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45988</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45862</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45996</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>44568</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46003</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>46003</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>46007</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46007</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>46007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>46007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44979</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45516</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46010</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44980</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45475</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46174</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45448</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>46017</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45399</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44524</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>46030</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46036</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>46038</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46099</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>46042</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46010</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>46091</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45552</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>46051</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46051</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45149</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46182</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>46182</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>46054</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44761</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>46059</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>46059</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46063</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45036</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45392</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>44719</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45169</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>46185</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>46086</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>46085</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44956</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>44824</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44910</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>46191</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45471</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45551</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45055</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45852</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45852</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45755</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>46099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45771</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46195</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>46104</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>46195</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>46107</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>46198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>44958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46111</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46111</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46111</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44557</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>46114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46113</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>46198</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45565</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46120</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46121</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46123</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46125</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46126</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46125</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45562</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46133</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>46133</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>46133</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45223</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45846</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45202</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45448</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>46136</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>46136</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>46209</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46206</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45565</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44888</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45244</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45636</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45448</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>46211</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>46212</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46212</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>46212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45735</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45566</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>44942</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46213</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>46213</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>46218</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45632</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46217</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46218</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>46220</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>46224</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46224</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46224</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45519</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45393</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46279</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45111</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45180</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45223</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44956</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46282</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45253</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46287</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>44494</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>46265</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46265</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46248</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46293</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>44848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45385</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45586</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45520</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45075</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45488</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45182</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>46295</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45734</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46254</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46253</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45572</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45478</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45614</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46300</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45562</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45789</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>44645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45771</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45140</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>45485</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46262</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45792</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>46261</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>46261</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45551</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46261</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45517</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46261</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46304</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>46261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>46304</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46304</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45803</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45800</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46309</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45805</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>46309</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45807</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45807</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>46301</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46309</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45664</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45742</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45811</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45824</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>46268</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45833</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45833</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45847</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45846</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45848</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45849</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45852</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45855</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45855</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45855</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45855</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45866</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45866</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45874</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45876</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45877</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45876</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45882</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45882</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45506</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45749</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45733</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45858</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45876</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45889</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46189</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45103</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         <v>45813</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -863,7 +863,7 @@
         <v>45412</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>45800</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>45785</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>45428</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45629</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45119</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1588,7 +1588,7 @@
         <v>45356</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>44526</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>44853</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>45225</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>46212</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>45202</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>46198</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>45756</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>45981</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45063</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>44957</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>45820</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3075,7 +3075,7 @@
         <v>45834</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3187,7 +3187,7 @@
         <v>46279</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>44902</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>45471</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3521,7 +3521,7 @@
         <v>45553</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3636,7 +3636,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45429</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>46047</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>46261</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>45418</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4304,7 +4304,7 @@
         <v>45840</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4415,7 +4415,7 @@
         <v>44603</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>46240</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4637,7 +4637,7 @@
         <v>44878</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>44855</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45534</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>45898</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45110</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>46150</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45302</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>45945</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>44994</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
         <v>46181</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5826,7 +5826,7 @@
         <v>45629</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>46209</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         <v>45629</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6156,7 +6156,7 @@
         <v>46238</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         <v>45198</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         <v>46261</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>45807</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45057</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>46308</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44606</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6926,7 +6926,7 @@
         <v>45756</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>46240</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>46258</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44810</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7407,7 +7407,7 @@
         <v>44629</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7485,7 +7485,7 @@
         <v>44834</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>44725</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44859</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>44845</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>44851</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>44587</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         <v>44974</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45622</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>45170</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         <v>45556</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8235,7 +8235,7 @@
         <v>45330</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8308,7 +8308,7 @@
         <v>45721</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         <v>45257</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45036</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
         <v>45097</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>45491</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8688,7 +8688,7 @@
         <v>45446</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>45125</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44876</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         <v>45125</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8985,7 +8985,7 @@
         <v>44889</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>45140</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44860</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9214,7 +9214,7 @@
         <v>45461</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>45547</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>45735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>45036</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>45351</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9594,7 +9594,7 @@
         <v>45198</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>45228</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>45228</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>44582</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>45013</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>45586</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10047,7 +10047,7 @@
         <v>45720</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>44742</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>45356</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10271,7 +10271,7 @@
         <v>45471</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10349,7 +10349,7 @@
         <v>45882</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10422,7 +10422,7 @@
         <v>45882</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10495,7 +10495,7 @@
         <v>45883</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45712</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45705</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>46139</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>45351</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>46136</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>46136</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45331</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>44889</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>46010</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45891</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45978</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>45988</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11542,7 +11542,7 @@
         <v>45893</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45140</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45855</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         <v>46136</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>45611</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>46136</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45295</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>46141</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45876</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>46136</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45898</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>46141</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45903</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45614</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46013</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45905</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45904</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46136</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>45678</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>45866</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45142</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13271,7 +13271,7 @@
         <v>45912</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13349,7 +13349,7 @@
         <v>45915</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13427,7 +13427,7 @@
         <v>45915</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13505,7 +13505,7 @@
         <v>45912</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45912</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45917</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45916</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>45916</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45483</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45917</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45757</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>45098</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46146</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>45917</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>46147</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14436,7 +14436,7 @@
         <v>45845</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46146</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46147</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>45845</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>44974</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>46189</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>46189</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45770</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15035,7 +15035,7 @@
         <v>46189</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15108,7 +15108,7 @@
         <v>46149</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45747</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15259,7 +15259,7 @@
         <v>46150</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>46153</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45936</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45936</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>46150</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45936</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15717,7 +15717,7 @@
         <v>46153</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>45938</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>45937</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45639</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>45672</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45253</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45642</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>44971</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>46155</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>45539</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45574</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45463</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45720</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>44888</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>44925</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44960</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45954</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45959</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45882</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>46107</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45161</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45069</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45505</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45614</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>45965</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45642</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45224</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45713</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>45491</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17929,7 +17929,7 @@
         <v>45966</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>45966</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>45962</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>46162</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18236,7 +18236,7 @@
         <v>46162</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
         <v>45217</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>44974</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18455,7 +18455,7 @@
         <v>45975</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18533,7 +18533,7 @@
         <v>45975</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18611,7 +18611,7 @@
         <v>44956</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>45977</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>45978</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18913,7 +18913,7 @@
         <v>46162</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18991,7 +18991,7 @@
         <v>46162</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>45980</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>45980</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>45981</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>45981</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>45600</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>45982</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>45561</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45982</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45642</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45642</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45988</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45988</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45988</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45862</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45996</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>44568</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>46003</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>46003</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>46007</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>46007</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>46007</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45755</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20866,7 +20866,7 @@
         <v>46007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20939,7 +20939,7 @@
         <v>46009</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45539</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>44979</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45516</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>46010</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>44980</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21392,7 +21392,7 @@
         <v>46174</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45475</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21548,7 +21548,7 @@
         <v>46174</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45448</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
         <v>45071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21777,7 +21777,7 @@
         <v>46017</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21855,7 +21855,7 @@
         <v>45399</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>44889</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22001,7 +22001,7 @@
         <v>44524</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22079,7 +22079,7 @@
         <v>46030</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22152,7 +22152,7 @@
         <v>46036</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22230,7 +22230,7 @@
         <v>46178</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22308,7 +22308,7 @@
         <v>46029</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>46038</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>46099</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22532,7 +22532,7 @@
         <v>46043</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22610,7 +22610,7 @@
         <v>46042</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22688,7 +22688,7 @@
         <v>46042</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>46042</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>46010</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22917,7 +22917,7 @@
         <v>46091</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45552</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23073,7 +23073,7 @@
         <v>46036</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23146,7 +23146,7 @@
         <v>46051</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23224,7 +23224,7 @@
         <v>46051</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>45149</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>46181</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23453,7 +23453,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>46182</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23609,7 +23609,7 @@
         <v>46182</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23687,7 +23687,7 @@
         <v>46055</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23765,7 +23765,7 @@
         <v>46054</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44761</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23916,7 +23916,7 @@
         <v>46059</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23989,7 +23989,7 @@
         <v>46059</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24062,7 +24062,7 @@
         <v>46063</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>45036</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24213,7 +24213,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24286,7 +24286,7 @@
         <v>45392</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>44719</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45169</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24520,7 +24520,7 @@
         <v>46185</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24598,7 +24598,7 @@
         <v>46086</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24676,7 +24676,7 @@
         <v>46085</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45169</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>44956</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>44824</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44910</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25061,7 +25061,7 @@
         <v>46191</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25134,7 +25134,7 @@
         <v>45471</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45551</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25285,7 +25285,7 @@
         <v>45055</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45852</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45852</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45755</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45796</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45169</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45315</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>46099</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45771</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46195</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>46104</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>46195</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>46196</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>46107</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>46198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>44958</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>46111</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26591,7 +26591,7 @@
         <v>46111</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>46111</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>44557</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45246</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>46114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46113</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>46198</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45565</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>46120</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46121</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27444,7 +27444,7 @@
         <v>45239</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>46123</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46125</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46126</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27756,7 +27756,7 @@
         <v>46125</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>45562</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>46133</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>46204</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>46133</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28224,7 +28224,7 @@
         <v>46133</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45223</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45846</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>45202</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45448</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28609,7 +28609,7 @@
         <v>46136</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28682,7 +28682,7 @@
         <v>46136</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>46209</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28828,7 +28828,7 @@
         <v>45036</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28901,7 +28901,7 @@
         <v>46206</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45565</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29057,7 +29057,7 @@
         <v>44888</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29130,7 +29130,7 @@
         <v>46206</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45244</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29286,7 +29286,7 @@
         <v>45636</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29364,7 +29364,7 @@
         <v>45448</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29442,7 +29442,7 @@
         <v>46211</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>46212</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>46212</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29666,7 +29666,7 @@
         <v>46212</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46211</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45735</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45566</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>44942</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>46213</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>46213</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>46218</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30270,7 +30270,7 @@
         <v>46218</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>45632</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>46217</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>46217</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30582,7 +30582,7 @@
         <v>46218</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30660,7 +30660,7 @@
         <v>46220</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30738,7 +30738,7 @@
         <v>46224</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>46224</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46224</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45519</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>45393</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>45253</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>46279</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45111</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31352,7 +31352,7 @@
         <v>45180</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31430,7 +31430,7 @@
         <v>46281</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45223</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>44956</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>46282</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>45253</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>45253</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45148</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>45198</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46287</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32195,7 +32195,7 @@
         <v>44494</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32268,7 +32268,7 @@
         <v>45103</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32341,7 +32341,7 @@
         <v>46265</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32419,7 +32419,7 @@
         <v>46265</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>46248</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>46293</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>46247</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32726,7 +32726,7 @@
         <v>44848</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32799,7 +32799,7 @@
         <v>45385</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45586</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45520</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45075</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>44748</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45488</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45182</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>46295</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45734</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         <v>46253</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33559,7 +33559,7 @@
         <v>46253</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46254</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>46253</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33783,7 +33783,7 @@
         <v>46253</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45572</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33934,7 +33934,7 @@
         <v>45478</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34007,7 +34007,7 @@
         <v>45614</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34080,7 +34080,7 @@
         <v>46300</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34153,7 +34153,7 @@
         <v>45562</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34231,7 +34231,7 @@
         <v>46300</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45789</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>44645</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45771</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45140</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34611,7 +34611,7 @@
         <v>45485</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34684,7 +34684,7 @@
         <v>46262</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34757,7 +34757,7 @@
         <v>45792</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>46261</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>46261</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34986,7 +34986,7 @@
         <v>45551</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46261</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>45517</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46261</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46304</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>45614</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>46261</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>46304</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46304</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>45803</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45800</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>46309</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45805</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>46309</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36033,7 +36033,7 @@
         <v>45807</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36111,7 +36111,7 @@
         <v>45807</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36189,7 +36189,7 @@
         <v>46301</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36262,7 +36262,7 @@
         <v>46309</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45664</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45742</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>45811</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36564,7 +36564,7 @@
         <v>45817</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36642,7 +36642,7 @@
         <v>45824</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36715,7 +36715,7 @@
         <v>46268</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36788,7 +36788,7 @@
         <v>45833</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45833</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36934,7 +36934,7 @@
         <v>45847</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45846</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45848</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45849</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45852</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45855</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45855</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>45855</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>45855</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>45866</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37694,7 +37694,7 @@
         <v>45866</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         <v>45874</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37845,7 +37845,7 @@
         <v>45874</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37918,7 +37918,7 @@
         <v>45875</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>45876</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         <v>45877</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45876</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38230,7 +38230,7 @@
         <v>45882</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38303,7 +38303,7 @@
         <v>45882</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38376,7 +38376,7 @@
         <v>45506</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45749</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45733</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38605,7 +38605,7 @@
         <v>45858</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38678,7 +38678,7 @@
         <v>45876</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38756,7 +38756,7 @@
         <v>45889</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38834,7 +38834,7 @@
         <v>46279</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>46189</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45103</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45412</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45852</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45852</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45785</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>45428</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>45629</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45119</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45356</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44853</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45225</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45202</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45820</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44957</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45834</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45471</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>46047</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45418</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45553</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44902</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44603</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45629</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46209</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44855</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>46238</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45807</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46308</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45110</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45534</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44994</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45629</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44878</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46240</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>46258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44629</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45883</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45586</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45471</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45330</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45891</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45228</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45893</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44980</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45903</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45562</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45912</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45491</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45912</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44942</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45962</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45566</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>46162</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45036</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45448</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45356</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45770</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45351</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45399</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44979</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45385</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>46099</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44910</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45539</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45224</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44524</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45516</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44889</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46178</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45954</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45125</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45142</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45959</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45217</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45965</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44876</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46191</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45735</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45975</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45975</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45978</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45978</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45980</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45980</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45982</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45446</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45981</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45981</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45642</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>46204</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45257</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45982</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44974</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45988</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46209</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45988</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45315</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45720</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>46211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>46211</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45253</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46212</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45862</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46212</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>46212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46213</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46213</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45551</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46217</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45996</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>46217</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46218</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46218</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45471</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45103</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46218</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>46220</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46224</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46224</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45572</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45478</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>46003</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45614</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45539</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46007</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45755</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44956</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46007</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>46009</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>46279</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45562</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46017</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46281</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45789</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46282</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45771</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45792</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45448</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45485</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45517</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46038</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45614</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>46287</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45140</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45800</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46247</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46091</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45803</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46051</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45805</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46054</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45807</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45807</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45664</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45742</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46293</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45811</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>46059</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46063</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46248</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>46265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45253</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46253</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44860</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>46253</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>46295</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>46253</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46085</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>46086</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45833</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46300</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45796</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45755</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45488</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>46099</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45483</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45846</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46104</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45848</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45847</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45849</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45852</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>46107</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45169</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45855</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45855</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45855</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46111</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46111</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46261</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45866</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45866</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>46261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46121</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>46120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46304</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46304</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46261</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46125</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46123</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46125</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46261</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>46126</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45876</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45875</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46304</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45876</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45877</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45712</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45882</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45882</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45882</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45882</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45882</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46133</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46133</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46133</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45622</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>46136</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>46262</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44889</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46309</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45846</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44557</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46309</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46140</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>46309</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45491</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45295</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46010</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45978</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>46136</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>46136</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>46013</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44974</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>46136</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45611</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45565</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45552</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45988</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>44971</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45705</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45876</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45351</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>46315</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46136</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46136</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45678</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46141</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44956</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46141</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46136</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45071</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46136</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45448</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46301</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46146</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46317</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46146</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46147</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46147</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46149</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>46150</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46150</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46189</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44888</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46153</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44960</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45747</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45461</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>46155</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>46107</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45161</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45882</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44956</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45519</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45642</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45642</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45125</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45182</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45632</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45149</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>44494</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45636</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45720</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45013</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>44889</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45244</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45111</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44568</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45757</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45036</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45561</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>45239</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45069</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44979</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45098</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45556</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45586</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45180</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45721</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45331</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45075</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45148</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45614</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45672</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44742</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45223</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44748</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45202</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>44974</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45246</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45642</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45392</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45547</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>44848</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45565</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45506</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45749</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45733</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45858</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45876</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>46279</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46189</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>

--- a/Översikt DOROTEA.xlsx
+++ b/Översikt DOROTEA.xlsx
@@ -601,7 +601,7 @@
         <v>45813</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -737,7 +737,7 @@
         <v>45103</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>45412</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>45852</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>45800</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>45852</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>45785</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1494,7 +1494,7 @@
         <v>45428</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1614,7 +1614,7 @@
         <v>45629</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>45119</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>45119</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>45356</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         <v>44526</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>44853</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>46212</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         <v>45225</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>45202</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2655,7 +2655,7 @@
         <v>46198</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>45756</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>45063</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>45820</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44957</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>45834</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         <v>45471</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3667,7 +3667,7 @@
         <v>45937</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>46047</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45418</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4003,7 +4003,7 @@
         <v>46296</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4114,7 +4114,7 @@
         <v>45840</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
         <v>46261</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4331,7 +4331,7 @@
         <v>45553</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44902</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>45429</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>44603</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>46240</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>45898</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         <v>45890</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>45629</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>45945</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>46209</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44855</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>46238</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45807</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>46261</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>46308</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6094,7 +6094,7 @@
         <v>45057</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6204,7 +6204,7 @@
         <v>46150</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>45110</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>45534</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44994</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45629</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44878</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6853,7 +6853,7 @@
         <v>45198</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45302</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7073,7 +7073,7 @@
         <v>44606</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7183,7 +7183,7 @@
         <v>45756</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>46240</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>46258</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44810</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>44629</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>44834</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44725</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44859</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>44845</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44851</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>44587</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45883</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>45586</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8351,7 +8351,7 @@
         <v>45471</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45734</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45330</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45891</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45228</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45893</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>44980</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>45898</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>45904</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45903</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9262,7 +9262,7 @@
         <v>44761</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45562</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45905</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45505</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9647,7 +9647,7 @@
         <v>46162</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9725,7 +9725,7 @@
         <v>46162</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9881,7 +9881,7 @@
         <v>45097</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         <v>45912</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10032,7 +10032,7 @@
         <v>45491</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>45912</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>45916</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44942</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10339,7 +10339,7 @@
         <v>45962</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>45915</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10490,7 +10490,7 @@
         <v>45915</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10568,7 +10568,7 @@
         <v>45916</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10646,7 +10646,7 @@
         <v>45566</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10719,7 +10719,7 @@
         <v>46162</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10875,7 +10875,7 @@
         <v>46162</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10948,7 +10948,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11026,7 +11026,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>45845</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11177,7 +11177,7 @@
         <v>45845</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11250,7 +11250,7 @@
         <v>45600</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>45639</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11401,7 +11401,7 @@
         <v>45036</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45448</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>45936</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11630,7 +11630,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45356</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45936</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45770</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>45351</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45938</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45399</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45937</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>44979</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>46174</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>46174</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>45385</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45574</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12619,7 +12619,7 @@
         <v>46099</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>44910</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45539</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>45253</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45253</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45224</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45055</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13228,7 +13228,7 @@
         <v>44824</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>44524</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>46181</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45516</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44889</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46178</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>46182</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13764,7 +13764,7 @@
         <v>45954</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>45125</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45142</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>46182</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45959</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14144,7 +14144,7 @@
         <v>45217</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45965</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45966</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44876</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>46191</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45735</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46195</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46195</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46196</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14987,7 +14987,7 @@
         <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15065,7 +15065,7 @@
         <v>45223</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45975</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15299,7 +15299,7 @@
         <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>45975</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>45978</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>45978</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15601,7 +15601,7 @@
         <v>45977</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45980</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15835,7 +15835,7 @@
         <v>45980</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45982</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45446</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45981</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45981</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45642</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>46204</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45713</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>45257</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16527,7 +16527,7 @@
         <v>45982</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16678,7 +16678,7 @@
         <v>46206</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16756,7 +16756,7 @@
         <v>44974</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>45988</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16902,7 +16902,7 @@
         <v>46209</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>45988</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17048,7 +17048,7 @@
         <v>45988</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>46206</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45315</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17277,7 +17277,7 @@
         <v>45720</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>46211</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17433,7 +17433,7 @@
         <v>46211</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17511,7 +17511,7 @@
         <v>45253</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>46212</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45862</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17730,7 +17730,7 @@
         <v>46212</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17803,7 +17803,7 @@
         <v>46212</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17881,7 +17881,7 @@
         <v>46213</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46213</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18027,7 +18027,7 @@
         <v>45551</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18100,7 +18100,7 @@
         <v>46217</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>45996</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>46217</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>46218</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18407,7 +18407,7 @@
         <v>46218</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>45471</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18563,7 +18563,7 @@
         <v>45103</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>46218</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18714,7 +18714,7 @@
         <v>46220</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18792,7 +18792,7 @@
         <v>46224</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>46224</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>45572</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46224</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19104,7 +19104,7 @@
         <v>45478</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19177,7 +19177,7 @@
         <v>46003</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19250,7 +19250,7 @@
         <v>45614</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19323,7 +19323,7 @@
         <v>46003</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19401,7 +19401,7 @@
         <v>45539</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>46007</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46007</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>46007</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45755</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19771,7 +19771,7 @@
         <v>44956</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>46007</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19917,7 +19917,7 @@
         <v>46009</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>46010</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>46279</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>45562</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
         <v>46017</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46281</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>45789</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>46030</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46282</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45771</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45792</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20765,7 +20765,7 @@
         <v>45448</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45485</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>44645</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45140</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>46036</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45551</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45517</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>46038</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>44582</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21442,7 +21442,7 @@
         <v>46042</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21520,7 +21520,7 @@
         <v>46042</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>46042</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>46029</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45614</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21822,7 +21822,7 @@
         <v>46043</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>46287</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45140</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45140</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22129,7 +22129,7 @@
         <v>45800</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22207,7 +22207,7 @@
         <v>46010</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22280,7 +22280,7 @@
         <v>46036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22353,7 +22353,7 @@
         <v>46247</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22426,7 +22426,7 @@
         <v>46091</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22504,7 +22504,7 @@
         <v>45803</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22582,7 +22582,7 @@
         <v>46051</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>46051</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46055</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>45805</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46054</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45807</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>45807</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45664</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>45742</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46293</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45811</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46265</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>46059</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>46059</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46063</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23810,7 +23810,7 @@
         <v>45817</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45520</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46248</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24039,7 +24039,7 @@
         <v>46265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24117,7 +24117,7 @@
         <v>45253</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>46072</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>46253</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>44860</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46253</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>46253</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>45824</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>46295</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>46253</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>46085</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24867,7 +24867,7 @@
         <v>46086</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>45833</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45833</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46300</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45796</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>46254</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>45755</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45488</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25476,7 +25476,7 @@
         <v>46099</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25549,7 +25549,7 @@
         <v>45483</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25627,7 +25627,7 @@
         <v>45846</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25700,7 +25700,7 @@
         <v>46104</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25773,7 +25773,7 @@
         <v>45848</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25851,7 +25851,7 @@
         <v>45847</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25929,7 +25929,7 @@
         <v>45849</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45852</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>46107</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45169</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>45855</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45855</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46111</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45855</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45855</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>46111</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>46111</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46261</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46113</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45866</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>45866</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46114</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>46261</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46121</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27381,7 +27381,7 @@
         <v>46120</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27459,7 +27459,7 @@
         <v>45874</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27532,7 +27532,7 @@
         <v>46304</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27605,7 +27605,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27678,7 +27678,7 @@
         <v>46304</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27751,7 +27751,7 @@
         <v>46261</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>46125</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27907,7 +27907,7 @@
         <v>46123</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>46125</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>46125</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>46261</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28219,7 +28219,7 @@
         <v>45874</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28292,7 +28292,7 @@
         <v>46126</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>45876</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28448,7 +28448,7 @@
         <v>45875</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>46304</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28599,7 +28599,7 @@
         <v>45876</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28677,7 +28677,7 @@
         <v>45877</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28755,7 +28755,7 @@
         <v>45712</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28833,7 +28833,7 @@
         <v>45882</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         <v>45882</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>45882</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29052,7 +29052,7 @@
         <v>45882</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29125,7 +29125,7 @@
         <v>45882</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>46133</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29276,7 +29276,7 @@
         <v>46133</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29354,7 +29354,7 @@
         <v>46133</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29432,7 +29432,7 @@
         <v>45622</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29510,7 +29510,7 @@
         <v>46136</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29583,7 +29583,7 @@
         <v>46262</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29656,7 +29656,7 @@
         <v>44889</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29729,7 +29729,7 @@
         <v>46309</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45846</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29880,7 +29880,7 @@
         <v>44557</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>46309</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30031,7 +30031,7 @@
         <v>46140</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30109,7 +30109,7 @@
         <v>44925</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45855</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30255,7 +30255,7 @@
         <v>46309</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45866</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30406,7 +30406,7 @@
         <v>45491</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30484,7 +30484,7 @@
         <v>46268</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30557,7 +30557,7 @@
         <v>45295</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46010</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>45978</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30776,7 +30776,7 @@
         <v>46136</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30849,7 +30849,7 @@
         <v>46136</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30922,7 +30922,7 @@
         <v>46013</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>44974</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31068,7 +31068,7 @@
         <v>45614</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31141,7 +31141,7 @@
         <v>44888</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31214,7 +31214,7 @@
         <v>46136</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31287,7 +31287,7 @@
         <v>45611</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45565</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45552</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45988</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>44971</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31662,7 +31662,7 @@
         <v>45705</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31735,7 +31735,7 @@
         <v>45876</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>45351</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>46315</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>46136</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>46139</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46136</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45678</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>46141</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>44956</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32412,7 +32412,7 @@
         <v>46141</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>44719</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>46136</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>46141</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>45071</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32787,7 +32787,7 @@
         <v>46136</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45448</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46301</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33011,7 +33011,7 @@
         <v>46146</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>46317</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46146</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46147</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>46147</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>44958</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>46149</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>46150</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46150</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46189</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>46189</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33849,7 +33849,7 @@
         <v>46189</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33922,7 +33922,7 @@
         <v>46153</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>44888</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>46153</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34151,7 +34151,7 @@
         <v>44960</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34224,7 +34224,7 @@
         <v>45747</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34297,7 +34297,7 @@
         <v>45461</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34375,7 +34375,7 @@
         <v>46155</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
         <v>46107</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45161</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45882</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>44956</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34760,7 +34760,7 @@
         <v>45519</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34833,7 +34833,7 @@
         <v>45642</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34906,7 +34906,7 @@
         <v>45642</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34979,7 +34979,7 @@
         <v>45125</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>45182</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35125,7 +35125,7 @@
         <v>45632</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>45149</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35354,7 +35354,7 @@
         <v>45198</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45170</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>44494</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45636</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45720</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45475</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45013</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>44889</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45244</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45111</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>44568</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45757</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36265,7 +36265,7 @@
         <v>45036</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36338,7 +36338,7 @@
         <v>45561</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36416,7 +36416,7 @@
         <v>45239</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45069</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>44979</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>45036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36718,7 +36718,7 @@
         <v>45098</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36791,7 +36791,7 @@
         <v>45556</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36864,7 +36864,7 @@
         <v>45586</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36942,7 +36942,7 @@
         <v>45180</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         <v>45721</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37098,7 +37098,7 @@
         <v>45331</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37171,7 +37171,7 @@
         <v>45075</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45036</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>45148</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>45614</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>45672</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44742</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>45223</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45169</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>45735</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45771</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37936,7 +37936,7 @@
         <v>44748</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38014,7 +38014,7 @@
         <v>45202</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>44974</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>45246</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>45642</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45392</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38399,7 +38399,7 @@
         <v>45547</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>44848</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>45565</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45506</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38701,7 +38701,7 @@
         <v>45749</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38774,7 +38774,7 @@
         <v>45733</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38852,7 +38852,7 @@
         <v>45858</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38925,7 +38925,7 @@
         <v>45876</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39003,7 +39003,7 @@
         <v>45889</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39081,7 +39081,7 @@
         <v>46279</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46189</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
